--- a/data/trans_camb/KIDM_C_3_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/KIDM_C_3_R-Edad-trans_camb.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -624,47 +624,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11,77</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2,27</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-2,05</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8,44</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5,08</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,01</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10,12</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3,73</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,97</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,26; 17,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,42; 7,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,71; 3,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,46; 13,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,08; 9,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,84; 4,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,1; 14,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,26; 6,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,39; 2,64</t>
         </is>
       </c>
     </row>
@@ -730,47 +730,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>192,01%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-33,41%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>211,14%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>127,16%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>202,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-19,38%</t>
         </is>
       </c>
     </row>
@@ -783,54 +783,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>51,67; 473,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-31,61; 182,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-85,13; 122,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>53,97; 673,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12,1; 480,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-76,91; 261,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>90,99; 427,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,83; 193,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-69,85; 77,18</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>12-15</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -840,47 +840,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7,84</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5,03</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1,27</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6,84</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6,88</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3,46</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7,33</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5,97</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-2,49</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,91; 13,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,49; 9,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,17; 3,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,46; 11,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,23; 11,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,48; -1,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,25; 10,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,89; 9,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,63; -0,1</t>
         </is>
       </c>
     </row>
@@ -946,47 +946,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>160,59%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>102,96%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-25,92%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>163,57%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>164,66%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-82,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>161,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>132,02%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-55,07%</t>
         </is>
       </c>
     </row>
@@ -999,54 +999,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>34,99; 439,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,35; 308,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-74,26; 90,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>33,17; 434,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>31,5; 430,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; -25,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>71,29; 319,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>48,27; 282,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-82,31; 1,53</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8-11</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1056,47 +1056,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11,77</t>
+          <t>9,85</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,27</t>
+          <t>3,76</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-2,05</t>
+          <t>-1,6</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8,44</t>
+          <t>7,58</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5,08</t>
+          <t>5,94</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,01</t>
+          <t>-2,18</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,12</t>
+          <t>8,7</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,73</t>
+          <t>4,87</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,97</t>
+          <t>-1,99</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,6; 18,58</t>
+          <t>5,73; 14,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 6,54</t>
+          <t>0,07; 6,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 3,32</t>
+          <t>-4,67; 1,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,49; 14,14</t>
+          <t>4,41; 10,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 9,92</t>
+          <t>2,93; 9,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 4,48</t>
+          <t>-4,45; 0,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,16; 14,35</t>
+          <t>6,32; 11,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 7,23</t>
+          <t>2,67; 7,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 2,83</t>
+          <t>-3,81; -0,08</t>
         </is>
       </c>
     </row>
@@ -1162,47 +1162,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>192,01%</t>
+          <t>183,6%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-33,41%</t>
+          <t>-29,76%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>211,14%</t>
+          <t>184,66%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>127,16%</t>
+          <t>144,66%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>-53,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>202,05%</t>
+          <t>184,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>103,33%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-19,38%</t>
+          <t>-42,1%</t>
         </is>
       </c>
     </row>
@@ -1215,500 +1215,66 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>57,67; 533,54</t>
+          <t>76,44; 371,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-37,56; 179,79</t>
+          <t>0,07; 172,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-84,76; 98,13</t>
+          <t>-69,66; 54,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>45,06; 650,14</t>
+          <t>76,31; 381,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,21; 477,9</t>
+          <t>51,34; 318,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-79,77; 204,49</t>
+          <t>-83,69; 18,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>91,11; 441,01</t>
+          <t>107,26; 303,67</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,17; 205,98</t>
+          <t>49,16; 186,77</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-67,83; 85,05</t>
+          <t>-68,43; 0,61</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>7,84</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>5,03</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-1,27</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>6,84</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>6,88</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-3,46</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,33</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>5,97</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>-2,49</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>2,96; 13,3</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>0,23; 9,89</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-5,31; 2,7</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2,87; 11,75</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2,39; 11,51</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-6,3; -1,29</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>4,26; 10,61</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>2,89; 9,59</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>-4,5; -0,1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n"/>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>160,59%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>102,96%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-25,92%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>163,57%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>164,66%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-82,87%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>161,96%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>132,02%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>-55,07%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>38,37; 408,99</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>0,48; 303,9</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>-77,68; 81,49</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>34,71; 469,33</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>32,37; 425,1</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; -17,38</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>71,13; 333,91</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>51,69; 301,3</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>-82,01; 1,54</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>9,85</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>3,76</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-1,6</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>7,58</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>5,94</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-2,18</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>8,7</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>4,87</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>-1,99</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n"/>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>5,8; 13,84</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>0,59; 7,06</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>-4,57; 1,59</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>4,44; 11,2</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>2,58; 9,44</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>-4,48; 0,24</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>6,11; 11,18</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>2,68; 7,24</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>-4,09; -0,14</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n"/>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>183,6%</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>70,03%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-29,76%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>184,66%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>144,66%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>-53,17%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>184,61%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>103,33%</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>-42,1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>74,14; 337,35</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>4,81; 178,07</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>-71,18; 42,34</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>77,78; 391,32</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>47,93; 331,01</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>-82,65; 15,25</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>102,56; 295,18</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>42,07; 190,47</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>-69,57; -2,86</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="7">
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A12:A15"/>
     <mergeCell ref="I1:K1"/>
-    <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_camb/KIDM_C_3_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/KIDM_C_3_R-Edad-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores de los que se han reido mucho o muchísimo otros menores (autopercepción menor)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,26; 17,8</t>
+          <t>5,71; 18,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 7,0</t>
+          <t>-2,6; 7,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 3,96</t>
+          <t>-6,99; 3,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,46; 13,81</t>
+          <t>3,47; 13,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 9,54</t>
+          <t>0,89; 9,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 4,99</t>
+          <t>-4,02; 4,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,1; 14,08</t>
+          <t>6,31; 14,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 6,77</t>
+          <t>0,08; 6,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 2,64</t>
+          <t>-4,02; 2,87</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>51,67; 473,25</t>
+          <t>57,04; 496,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-31,61; 182,81</t>
+          <t>-30,94; 207,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-85,13; 122,16</t>
+          <t>-85,35; 108,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53,97; 673,62</t>
+          <t>44,05; 600,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,1; 480,21</t>
+          <t>5,69; 440,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-76,91; 261,25</t>
+          <t>-81,45; 233,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,99; 427,2</t>
+          <t>87,64; 437,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,83; 193,34</t>
+          <t>-1,76; 192,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-69,85; 77,18</t>
+          <t>-65,06; 88,89</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,91; 13,07</t>
+          <t>3,05; 13,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 9,67</t>
+          <t>0,38; 10,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 3,1</t>
+          <t>-5,1; 2,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,46; 11,4</t>
+          <t>2,77; 11,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 11,25</t>
+          <t>2,69; 11,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,48; -1,21</t>
+          <t>-6,52; -1,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,25; 10,66</t>
+          <t>4,24; 10,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,89; 9,46</t>
+          <t>2,59; 9,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,63; -0,1</t>
+          <t>-4,78; -0,11</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>34,99; 439,24</t>
+          <t>40,29; 423,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,35; 308,82</t>
+          <t>2,93; 316,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-74,26; 90,12</t>
+          <t>-78,2; 96,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33,17; 434,85</t>
+          <t>40,32; 422,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,5; 430,76</t>
+          <t>38,39; 431,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -25,98</t>
+          <t>-100,0; -20,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,29; 319,23</t>
+          <t>65,78; 308,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>48,27; 282,87</t>
+          <t>37,54; 263,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-82,31; 1,53</t>
+          <t>-80,15; 8,66</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,73; 14,1</t>
+          <t>6,09; 13,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 6,93</t>
+          <t>0,29; 7,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 1,92</t>
+          <t>-4,77; 1,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,41; 10,81</t>
+          <t>4,04; 11,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,93; 9,14</t>
+          <t>2,88; 9,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 0,2</t>
+          <t>-4,44; 0,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,32; 11,51</t>
+          <t>6,02; 11,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,67; 7,25</t>
+          <t>2,42; 7,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,81; -0,08</t>
+          <t>-3,98; 0,02</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>76,44; 371,89</t>
+          <t>83,17; 370,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,07; 172,09</t>
+          <t>3,71; 191,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-69,66; 54,38</t>
+          <t>-70,81; 51,31</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>76,31; 381,76</t>
+          <t>72,29; 394,95</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>51,34; 318,32</t>
+          <t>51,27; 320,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-83,69; 18,19</t>
+          <t>-83,33; 17,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>107,26; 303,67</t>
+          <t>101,83; 290,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>49,16; 186,77</t>
+          <t>38,93; 186,75</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-68,43; 0,61</t>
+          <t>-69,97; 1,1</t>
         </is>
       </c>
     </row>
